--- a/out/results.xlsx
+++ b/out/results.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QFaaS is a quantum Function-as-a-Service framework proposed to address challenges from the diversity of quantum programming languages and hardware platforms. Its objective is to leverage serverless and software engineering approaches to advance practical quantum computing and ease the quantum software transition for traditional engineers.</t>
+          <t>QFaaS is a Quantum Function-as-a-Service framework proposed to address challenges from the diversity of quantum programming languages and hardware platforms. It aims to use a serverless model and software engineering approaches to advance practical quantum computing and ease the transition for traditional engineers.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Algorithm 2: QFaaS Function Invocation Input : req: User request data (JSON), fnEndpoint: API endpoint of function</t>
+          <t>Input : req: User request data (JSON), fnEndpoint: API endpoint of function</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>QFaaS is designed around modularity, using a microservice and everything-as-a-service approach so modules can be extended independently. It also aims to unify hybrid quantum-classical development for quantum cloud computing through containerized functions and DevOps-oriented platform components.</t>
+          <t>The framework is designed around modular, pluggable components inspired by microservices and the everything-as-a-service paradigm to simplify extension and maintenance. It also aims to unify hybrid quantum-classical serverless development across multiple quantum SDKs, simulators, and cloud providers while incorporating containerization and DevOps-oriented capabilities.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The framework uses Kubernetes for container orchestration and MongoDB as a NoSQL database. It supports quantum languages and SDKs including Qiskit, Q#, Cirq, and Braket, and targets simulators plus cloud providers such as IBM Quantum and Amazon Braket.</t>
+          <t>The implementation uses Kubernetes for container orchestration, MongoDB as a NoSQL database, and supports quantum languages/SDKs including Qiskit, Q#, Cirq, and Braket. It targets execution on simulators and quantum cloud providers such as IBM Quantum and Amazon Braket.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.2.4 Quantum Cloud Layer. This layer is the external part, indicating the quantum cloud providers (such as IBM Quantum and Amazon Braket), where the quantum job can be executed in a physical quantum computer.</t>
+          <t>This layer is the external part, indicating the quantum cloud providers (such as IBM Quantum and Amazon Braket), where the quantum job can be executed in a physical quantum computer.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QuantumPath is a quantum software development platform intended to support the design, implementation, and execution of quantum software applications. It is also described as supporting the management of quantum software development projects.</t>
+          <t>QuantumPath is a quantum software development platform intended to support the design, implementation, and execution of quantum software applications. It is also described as supporting the management of quantum software development projects while remaining agnostic to different quantum technologies.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>both the circuit editor and the annealing editor generate a proprietary metalanguage that is agnostic to each vendor's quantum technology</t>
+          <t>boththecircuiteditorandtheannealingeditorgenerateaproprietarymetalanguagethatisagnostic toeachvendor'squantumtechnology.</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>The corresponding metalanguage is then transpiled in design time to the programming language supported by each manufacturer and executed in the target environment.</t>
+          <t>Thecorrespondingmetalanguageisthentranspiledindesigntimetotheprogramming language supported by each manufacturer and executed in the target environment.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Section 4 offers an example of QuantumPath use</t>
+          <t>QuantumPathhasbeentestedinrecentmonthsbyalimitednumberofcustomers,invitedfromthehealthandfinance sectors.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>The architecture is guided by principles such as agnosticism, extensibility, integration, independency, optimisation, scalability, security, usability, and software-engineering support. It is positioned as a platform to support both the development and execution of quantum software, including hybrid interconnection with classical systems.</t>
+          <t>The architecture is guided by principles including agnosticism, extensibility, integration, independency, optimisation, scalability, security, usability, and software-engineering support. It is positioned as a platform architecture plus supporting tools for developing and executing quantum software, with emphasis on hybrid-system interconnection and decoupled, scalable backend processing.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>The document mentions QuantumPath, qSOA architecture, Connection Points, BoxFlows, WEBINARAnneal, and a "dwave_ExactSolver_simulator" device. It also references an enterprise backend and an AI-based system using telemetry data, but specific implementation languages or frameworks are not stated.</t>
+          <t>Not stated.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing.</t>
+          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;"</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>In developing QuantumPath, our aim is tofulfilcertainprinciplessuchas:agnosticism,extensibility,integration,independency,optimisation,scalability,security,usabilityandsoftwareengineering support.</t>
+          <t>"when decidingonwhichcomputeritismoreconvenientto runaquantumprogram,astheydifferinefficiency,errortolerance,andcost,"</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;</t>
+          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;"</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>"Device":"dwave_ExactSolver_simulator",</t>
+          <t>"Device":"dwave_ExactSolver_simulator"</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing.</t>
+          <t>"A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing."</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing.</t>
+          <t>"A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing."</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;andwillalsocollectallthetelemetryfrom theprocess,</t>
+          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;andwillalsocollectallthetelemetryfrom theprocess,"</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -995,14 +995,10 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>Amorecompletedemonstration,walkingtheuserthroughtwoexamplesofquantum-gatesbasedcircuitdesignand annealing-basedoptimisation,canbefoundintheaQuantumYouTubechannel.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="b">
         <v>1</v>
       </c>
@@ -1025,15 +1021,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>iQuantum is a versatile and lightweight simulation framework designed to model quantum computing environments for quantum software and system research, with a focus on resource management and orchestration. It is intended to help address challenges in reproducing experimental results and comparing the performance of different algorithms or applications when no standard simulator is available.</t>
+          <t>iQuantum is a versatile, lightweight simulation framework/toolkit for modeling hybrid quantum computing environments to support quantum software and system research, with a focus on resource management and orchestration. It is also presented as a toolkit for prototyping and problem formulation in quantum resource management.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>OS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>asanopen-source toolundertheGPL-3.0license.</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>itprovidessupportfor externaldatasets,accommodatingbothOpenQASMfilesforquantumtasksandquantumcomputercalibrationdatafor quantumsystems.</t>
+          <t>itprovidessupportfor externaldatasets,accommodatingbothOpenQASMfilesforquantumtasksandquantumcomputercalibrationdata for quantumsystems.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1062,10 +1062,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Then, whenthesimulationisinitialized,itwillfirstsetuptheenvironmentwithallpre-definedentities.</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>EX</t>
@@ -1073,17 +1077,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>WevalidateandevaluateiQuantumindifferentscenariosusingtrustworthydatasets,includingIBMQuantum 13 calibration data for quantum systems and the MQT Bench dataset34 for the workload.</t>
+          <t>Through rigorous empiricalvalidation and evaluations usinglarge-scalequantumworkloaddatasets,wedemonstratetheflexibilityand applicability of our toolkit in various use cases.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>The architecture is guided by a layered, modular design intended to support hybrid quantum-classical environments and to extend the toolkit through refactoring and added features. It emphasizes modeling, simulation, and evaluation of resource-management strategies across a cloud-edge continuum.</t>
+          <t>The toolkit follows a layered, modular architecture and was improved through refactoring and feature additions to support both quantum and hybrid quantum-classical simulation. It is designed around discrete-event simulation and resource-management evaluation in cloud-edge hybrid environments.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>The implementation is based on a discrete-event simulation approach and leverages the CloudSim toolkit. It also states compatibility with Python-Java brokers such as Py4J for integrating machine-learning-based policies.</t>
+          <t>Implemented using a discrete-event simulation approach and leveraging the core components of the CloudSim toolkit; the design also includes CloudSim-derived classical entities such as VMs, containers, and classical tasks.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1093,7 +1097,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>iQuantumisdesignedwithamodulararchitecturethatcomprisesfivemainlayers:coresimulation,physical,logical, middleware, and resource management.</t>
+          <t>Thegatewaylayercomprisesintermediarycomponents,includinggatewaysandbrokers,whichfacilitatecommunication andtaskorchestrationbetweencloudandedgecomputationcomponents.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1103,7 +1107,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>All elements in these layers are implemented to demonstrate the functionality and usefulness of our toolkit in modeling, simulating, and evaluating resource management strategies for hybrid quantum-classicalcomputinginthecloud-edgecontinuum.</t>
+          <t>Thebrokers,namelyQCloudBroker,QEdgeBroker,CCloudBroker,andCEdgeBroker,thenperformthetaskschedulingbasedontheresourcemanagementpolicies inthesystem.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1142,10 +1146,14 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>adatacentercanbeseenasacollection(orcluster)ofmultiplecomputingnodes(QNodesorCNodes), whichcanbecoordinatedtoperformacommontask.</t>
+        </is>
+      </c>
       <c r="AI4" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1154,10 +1162,14 @@
       <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>IniQuantum,agateway(cloudoredgegateway)isacommunicationinterfacebetweendatacenterbrokersandthelayerbelow.</t>
+        </is>
+      </c>
       <c r="AM4" t="inlineStr">
         <is>
           <t>No</t>
@@ -1165,7 +1177,7 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>"For modeling large-scale quantum task workloads, we used MQT Bench34 and extracted features of quantum circuits for 28differentquantumalgorithms"</t>
+          <t>"For modeling large-scale quantum task workloads, we used MQT Bench34 and extracted features of quantum circuits for 28differentquantumalgorithmsintofoursetsasshowninTable 5."</t>
         </is>
       </c>
       <c r="AO4" t="b">
@@ -1190,7 +1202,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>staq is a full-stack quantum compiler/software toolkit for the openQASM language. Its goal is to provide transformation, optimization, and compilation tools on a common language and target multiple simulation and hardware execution platforms.</t>
+          <t>staq is a full-stack quantum compiler toolkit designed as a collection of small command-line tools for tasks such as optimization, translation, and physical mapping on quantum devices with restricted connectivity. It aims to provide complex functionality by composing minimalist tools around a single textual language, openQASM.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1217,64 +1229,56 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Multiple</t>
+          <t>QSC</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>The primary goal is to provide a suite of transformation, optimization and compila tion tools that can operate on a single, common language, and output to a number of diﬀerent simulation and hardware execution platforms.</t>
+          <t>Finally, staq can generate quantum code in a variety of formats that encompass many of the currently available quantu m platforms [15, 18, 19, 9, 10, 12].</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>EX</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>To assess the performance of staq, we compare it against the well-known software toolkit and compiler Qiskit [19].</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>staq follows a UNIX-style design that emphasizes small, single-purpose tools composed through pipelines, and it operates directly on QASM syntax trees with a Clang-inspired visitor-based analysis and transformation approach.</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>The toolkit is implemented in standard C++ using the C++17 standard, works directly on QASM syntax trees, includes Visitor classes for AST traversal and splicing, and supports classical logic specified in Verilog within openQASM code.</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>staq achieves complex functionality via combining (piping) sma ll tools, each of which performs a single task using the most adv anced current state-of-the-art methods.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>EX</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>The remainder of this paper describes the staq toolkit and its functionality and uses cases while providing a set of benchmarks (Section 2),</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>staq follows a UNIX-style philosophy of composing many small single-purpose tools, emphasizing modularity and source-to-source transformations on syntax trees so tools can be combined flexibly. Its architecture favors minimal independent changes by each tool and configurable pass ordering through command-line composition.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Implemented in standard C++ using the C++17 standard. The architecture is described as using a Clang-style syntax-tree-based approach, and it works with openQASM and Verilog while generating code for multiple quantum platform formats.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>staq achieves complex functionality via combining (piping) sma ll tools, each of which performs a single task</t>
-        </is>
-      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>The main command line compiler staq - oﬀers a ﬂexible pass registration system, whereby passes are given via command-line arguments and are executed in the order given.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1282,19 +1286,15 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>staq can generate quantum code in a variety of formats that encompass many of the currently available quantu m platforms</t>
+          <t>Finally, staq can generate quantum code in a variety of formats that encompass many of the currently available quantu m platforms [15, 18, 19, 9, 10, 12].</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>staq can generate quantum code in a variety of formats that encompass many of the currently available quantu m platforms</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1332,17 +1332,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>the staq software package also includes a suite of lightweight command line tools which can be chained together using Unix-st yle pipelines</t>
+          <t>T ool suite In addition to a single compiler, the staq software package also includes a suite of lightweight command line tools which can be chained together using Unix-st yle pipelines to perform a range of compilation tasks.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>"The main optimization of the staq compiler is an extended implementation of Fang and Chen's T -count optimization4 algorithm [27]."</t>
+          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
         </is>
       </c>
       <c r="AO5" t="b">
@@ -1360,7 +1360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1382,6 +1382,72 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>evidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>layout generation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>eager</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>layout generation</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>best-fit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>layout generation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,7 +1505,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Access to quantum cloud services is limited from the authors' region, restricting which providers they can currently demonstrate.</t>
+          <t>Access to quantum cloud services is limited from the authors' region, restricting which providers they can currently demonstrate with.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1471,7 +1537,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Diversity of quantum programming languages and hardware platforms creates challenges for quantum software engineering.</t>
+          <t>The diversity of quantum programming languages and hardware platforms creates challenges for quantum software engineering.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1503,7 +1569,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantum computing has a steep learning curve due to a fundamental paradigm shift from classical computing.</t>
+          <t>Quantum computing has a steep learning curve for developers, making adoption difficult.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1513,7 +1579,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"the learning curve of quantum computing is very pronounced."</t>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1523,7 +1589,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>"we have to recognise that the learning curve of quantum computing is very pronounced."</t>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1611,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"Quantum software platforms and toolkits are difficult to use in industry."</t>
+          <t>Quantum software platforms and toolkits are difficult to use in industry.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1555,7 +1621,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>"they do not bring much context support to the generation of quantum algorithms."</t>
+          <t>they do not bring much context support to the generation of quantum algorithms.</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1643,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>"released in different versions (not always compatible with the previous ones), and some features have been discontinued - with the result that we have had to modify our platform."</t>
+          <t>Several of the tools we have integrated into QuantumPath have been released in different versions (not always compatible with the previous ones), and some features have been discontinued - with the result that we have had to modify our platform.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1587,7 +1653,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>"with the result that we have had to modify our platform."</t>
+          <t>with the result that we have had to modify our platform.</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1665,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Offering design services for both gate-based quantum and annealing systems on one integrated platform has been difficult.</t>
+          <t>Providing integrated design services for both gate-based quantum and annealing systems on one platform has been difficult.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1609,7 +1675,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>"Design services for both gate-based quantum and annealing systems have been difficult to offer on the same platform and in an integrated manner."</t>
+          <t>Design services for both gate-based quantum and annealing systems have been difficult to offer on the same platform and in an integrated manner.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1619,7 +1685,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>"have been difficult to offer on the same platform and in an integrated manner."</t>
+          <t>have been difficult to offer on the same platform and in an integrated manner.</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1697,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Annealing-based system design needs a more user-friendly interface beyond mathematical formula definitions to guide users and prevent errors.</t>
+          <t>Annealing-based system design needs a more user-friendly interface to guide users and reduce errors.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1641,7 +1707,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors."</t>
+          <t>it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1651,7 +1717,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>"we believe that it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors."</t>
+          <t>which can guide the user and control possible errors.</t>
         </is>
       </c>
     </row>
@@ -1663,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iQuantum does not directly simulate quantum physical phenomena such as superposition and entanglement, limiting it to a high-level abstract simulation of operational aspects.</t>
+          <t>iQuantum does not directly simulate quantum physical phenomena such as superposition and entanglement, limiting it to high-level operational simulation.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1695,17 +1761,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Resource provisioning policies mainly target classical resources because quantum resource virtualization or partitioning is not yet mature.</t>
+          <t>Evaluating the impact of quantum errors on execution results is outside the scope of the study.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scalability</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>resource provisioning policies are mainly for classical resources, as quantum resource virtualization or partitioning is not yet mature.</t>
+          <t>supporting the evaluation of the quantum errors impacts on quantum execution results is not within the scope of our study</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1715,7 +1781,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>However, it can be extended in future releases to adapt to the current nature of quantum technology.</t>
+          <t>However, it is important to note that supporting the evaluation of the quantum errors impacts on quantum execution results is not within the scope of our study and can be considered for future extension.</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1793,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Circuit depth is only an approximate metric, so more precise methods are recommended for measuring circuit layers when adapting to CLOPS benchmarking.</t>
+          <t>Circuit depth is only an approximate metric, so more precise methods are needed for measuring CLOPS-related circuit layers.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks</t>
+          <t>circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks to adapt to the measurement of the CLOPS metric for quantum nodes.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1759,17 +1825,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Repeated fixpoint simplification can make optimization quadratic in program length and may be prohibitively costly.</t>
+          <t>The scalability of staq's optimization algorithms needs improvement as qubit count increases.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Scalability</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>"this extra cos t making the optimization quadratic in the length of the program - may b e prohibitive."</t>
+          <t>It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1779,7 +1845,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>"In some cases this extra cos t making the optimization quadratic in the length of the program - may b e prohibitive."</t>
+          <t>It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases.</t>
         </is>
       </c>
     </row>
@@ -1791,27 +1857,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The scalability of optimization algorithms worsens as the number of qubits increases and requires further improvement.</t>
+          <t>Hardware mapping results were mixed, and Qiskit usually produced better CNOT counts than staq.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scalability</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>"It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases."</t>
+          <t>Qiskit outperformed staq in terms of CNOT counts in the majority of cases.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Implicit anecdotal</t>
+          <t>Explicit empirical</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>"It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases."</t>
+          <t>the experimental results for hardware mapping were mixed.</t>
         </is>
       </c>
     </row>
@@ -1823,17 +1889,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hardware mapping support is limited in the reported evaluation to circuits that fit on IBM's 20-qubit Tokyo chip.</t>
+          <t>Some benchmark circuits could not be included because only circuits that fit on IBM's 20-qubit Tokyo chip were reported.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Scalability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>"only the benchmark circuits which ﬁt onto the chip are re ported in Table 2."</t>
+          <t>only the benchmark circuits which ﬁt onto the chip are re ported in Table 2.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1843,7 +1909,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>"IBM's 20 qubit Tokyo chip was se lected as the target architecture, and as such only the benchmark circuits which ﬁt onto the chip are re ported in Table 2."</t>
+          <t>IBM's 20 qubit Tokyo chip was se lected as the target architecture, and as such only the benchmark circuits which ﬁt onto the chip are re ported in Table 2.</t>
         </is>
       </c>
     </row>
@@ -1855,91 +1921,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hardware mapping quality is inconsistent: although faster, staq often produces worse CNOT counts than Qiskit.</t>
+          <t>Local ancilla allocation is non-standard QASM and is not supported by most QPUs.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Interoperability</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>"Qiskit outperformed staq in terms of CNOT counts in the majority of cases."</t>
+          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs,</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Explicit empirical</t>
+          <t>Implicit anecdotal</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>"While the Steiner mapping algorithm with best-fit initial layout was consistently orders of magnitude faster than Qisk it's default mapping algorithm, Qiskit outperformed staq in terms of CNOT counts in the majority of cases."</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>T003</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Some cases are pathological for the underlying Gray-synth algorithm, indicating reliability or robustness issues in synthesis outcomes.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Reliability</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>"many of the cases where Qiskit outperformed staq appear to be pathological cases for the underlying Gray-synth algorithm [25]."</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Implicit anecdotal</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>"many of the cases where Qiskit outperformed staq appear to be pathological cases for the underlying Gray-synth algorithm [25]."</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>T003</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Local ancilla allocation is non-standard QASM and is not supported by most QPUs, requiring automatic ancilla management during compilation.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Interoperability</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>"As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs"</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Implicit anecdotal</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>"As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs, staq performs automatic ancilla management during the inlining phase of co mpilation."</t>
+          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs,</t>
         </is>
       </c>
     </row>

--- a/out/results.xlsx
+++ b/out/results.xlsx
@@ -10,6 +10,7 @@
     <sheet name="tools" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="algorithms" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="challenges" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="validation_errors" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -628,34 +629,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T000</t>
+          <t>T_1cd9410310</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>.\data\QFaaS _ A serverless Function-as-a-Service Framework for Quantum Computing.pdf</t>
+          <t>.\data\iQuantum _ A toolkit for modeling and simulation of quantum computing environments.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>QFaaS</t>
+          <t>iQuantum</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>QFaaS is a Quantum Function-as-a-Service framework proposed to address challenges from the diversity of quantum programming languages and hardware platforms. It aims to use a serverless model and software engineering approaches to advance practical quantum computing and ease the transition for traditional engineers.</t>
+          <t>The tool is a versatile and lightweight simulation framework designed to model quantum computing environments and support quantum software and system research, with a focus on resource management and orchestration. It aims to address the lack of a standard simulator for reproducing experiments and comparing algorithm or application performance.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Software Availability: We will release the QFaaS framework in open source</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -669,7 +666,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Input : req: User request data (JSON), fnEndpoint: API endpoint of function</t>
+          <t>itprovidessupportfor externaldatasets,accommodatingbothOpenQASMfilesforquantumtasksandquantumcomputercalibrationdatafor quantumsystems.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -679,19 +676,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Output :result: Computation result data, or jobID: Job ID for later tracking</t>
+          <t>OurtoolkitalsofacilitatesdataimportingandexportinginacommonCSVformat, enablingfurther investigationandanalysis.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>FA</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>which supports to automate the quantum software development cycle, from quantum environment setup to hybrid quantum-classical function deployment.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
           <t>EX</t>
@@ -699,17 +692,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>We present two practical use cases and perform the evaluations on quantum computers and simulators</t>
+          <t>WevalidateandevaluateiQuantumindifferentscenariosusingtrustworthydatasets,includingIBMQuantum 13 calibration data for quantum systems and the MQT Bench dataset34 for the workload.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>The framework is designed around modular, pluggable components inspired by microservices and the everything-as-a-service paradigm to simplify extension and maintenance. It also aims to unify hybrid quantum-classical serverless development across multiple quantum SDKs, simulators, and cloud providers while incorporating containerization and DevOps-oriented capabilities.</t>
+          <t>The architecture is described as a layered, modular design that was extensively refactored and extended to support both quantum and hybrid quantum-classical simulation. It is intended to model, simulate, and evaluate resource management strategies in cloud-edge hybrid quantum environments using a discrete-event simulation approach.</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>The implementation uses Kubernetes for container orchestration, MongoDB as a NoSQL database, and supports quantum languages/SDKs including Qiskit, Q#, Cirq, and Braket. It targets execution on simulators and quantum cloud providers such as IBM Quantum and Amazon Braket.</t>
+          <t>The implementation is based on the CloudSim toolkit and uses a discrete-event simulation approach. It also mentions compatibility with Python-Java brokers such as Py4J for integrating machine learning-based policies.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -719,7 +712,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>We employed Kubernetes to orchestrate all the pods (the container-based unit of Kubernetes) for the QFaaS function across all cluster nodes.</t>
+          <t>iQuantumisdesignedwithamodulararchitecturethatcomprisesfivemainlayers:coresimulation,physical,logical, middleware, and resource management.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -729,19 +722,15 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>We break down QFaaS into six components: the QFaaS Core APIs and API Gateway, the Application Deployment Layer, the Classical Cloud Layer, the Quantum Cloud Layer, the Monitoring Layer, and the User Interface.</t>
+          <t>All elements in these layers are implemented to demonstrate the functionality and usefulness of our toolkit in modeling, simulating, and evaluating resource management strategies for hybrid quantum-classicalcomputinginthecloud-edgecontinuum.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>We design QFaaS as a unified quantum computing framework by supporting well-known quantum languages and software development kits (Qiskit, Q#, Cirq, and Braket), executing the quantum tasks on multiple simulators and quantum cloud providers (IBM Quantum and Amazon Braket).</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -749,7 +738,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>This layer is the external part, indicating the quantum cloud providers (such as IBM Quantum and Amazon Braket), where the quantum job can be executed in a physical quantum computer.</t>
+          <t>iQuantum'scompatibilitywithPython-Javabrokers,suchasPy4J, * allowsforstraightforwardintegrationof machine learning-based policies.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +754,7 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>All quantum SDKs and languages have their built-in quantum simulator, which can run directly inside a pod at the Kubernetes cluster.</t>
+          <t>WedevelopediQuantumusingthe discrete-eventsimulationapproach,leveragingthecorecomponentsoftheCloudSim toolkit.</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -776,48 +765,40 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Each function will be run on a pod and could be scaled up horizontally by replicating the original pod.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>We break down QFaaS into six components: the QFaaS Core APIs and API Gateway, the Application Deployment Layer, the Classical Cloud Layer, the Quantum Cloud Layer, the Monitoring Layer, and the User Interface.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>We break down QFaaS into six components: the QFaaS Core APIs and API Gateway, the Application Deployment Layer, the Classical Cloud Layer, the Quantum Cloud Layer, the Monitoring Layer, and the User Interface.</t>
-        </is>
-      </c>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr"/>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>For modeling large-scale quantum task workloads, we used MQT Bench34 and extracted features of quantum circuits for 28differentquantumalgorithms</t>
+        </is>
+      </c>
       <c r="AO2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -832,7 +813,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>QuantumPath is a quantum software development platform intended to support the design, implementation, and execution of quantum software applications. It is also described as supporting the management of quantum software development projects while remaining agnostic to different quantum technologies.</t>
+          <t>QuantumPath is a quantum software development platform intended to support the design, implementation, and execution of quantum software applications. It is also described as supporting the management of quantum software development projects while remaining agnostic across quantum technologies.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -842,7 +823,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Although it is not open-source software, it can be accessed in a very advantageous way if you are part of the aQuantum network</t>
+          <t>Although it is not open-source software</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -868,7 +849,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>boththecircuiteditorandtheannealingeditorgenerateaproprietarymetalanguagethatisagnostic toeachvendor'squantumtechnology.</t>
+          <t>both the circuit editor and the annealing editor generate a proprietary metalanguage</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -878,7 +859,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Thecorrespondingmetalanguageisthentranspiledindesigntimetotheprogramming language supported by each manufacturer and executed in the target environment.</t>
+          <t>The corresponding metalanguage is then transpiled in design time to the programming language supported by each manufacturer and executed in the target environment.</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -888,17 +869,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>QuantumPathhasbeentestedinrecentmonthsbyalimitednumberofcustomers,invitedfromthehealthandfinance sectors.</t>
+          <t>QuantumPath has been tested in recent months by a limited number of customers, invited from the health and finance sectors.</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>The architecture is guided by principles including agnosticism, extensibility, integration, independency, optimisation, scalability, security, usability, and software-engineering support. It is positioned as a platform architecture plus supporting tools for developing and executing quantum software, with emphasis on hybrid-system interconnection and decoupled, scalable backend processing.</t>
+          <t>The architecture is guided by principles including agnosticism, extensibility, integration, independency, optimisation, scalability, security, usability, and software-engineering support. It is presented as a platform to support both the development and execution of quantum software, including hybrid interconnection with classical systems.</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Not stated.</t>
+          <t>The platform includes BoxFlows, WEBINARAnneal, a "dwave_ExactSolver_simulator", and a qSOA architecture. It also includes an enterprise backend and a telemetry system database, with AI-based support for platform selection.</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -918,7 +899,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;"</t>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -928,7 +909,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>"when decidingonwhichcomputeritismoreconvenientto runaquantumprogram,astheydifferinefficiency,errortolerance,andcost,"</t>
+          <t>Finally,wewouldliketohighlightanothersignificantissuewhendecidingonwhichcomputeritismoreconvenientto runaquantumprogram,astheydifferinefficiency,errortolerance,andcost,andmuchdependsonthetypeofalgorithm orcircuittobeexecuted.</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -938,7 +919,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;"</t>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -964,7 +945,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>"A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing."</t>
+          <t>A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing.</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -974,7 +955,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>"A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing."</t>
+          <t>A backend that - by design-contemplatessecurity,highavailability,loadbalancingandasynchronouscustomerprocessing.</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -984,7 +965,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>"Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;andwillalsocollectallthetelemetryfrom theprocess,"</t>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;andwillalsocollectallthetelemetryfrom theprocess,</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -995,10 +976,14 @@
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>"walkingtheuserthroughtwoexamplesofquantum-gatesbasedcircuitdesignand annealing-basedoptimisation"</t>
+        </is>
+      </c>
       <c r="AO3" t="b">
         <v>1</v>
       </c>
@@ -1006,22 +991,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>.\data\iQuantum _ A toolkit for modeling and simulation of quantum computing environments.pdf</t>
+          <t>.\data\QFaaS _ A serverless Function-as-a-Service Framework for Quantum Computing.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>iQuantum</t>
+          <t>QFaaS</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>iQuantum is a versatile, lightweight simulation framework/toolkit for modeling hybrid quantum computing environments to support quantum software and system research, with a focus on resource management and orchestration. It is also presented as a toolkit for prototyping and problem formulation in quantum resource management.</t>
+          <t>QFaaS is a proposed quantum Function-as-a-Service framework intended to reduce quantum software engineering challenges, particularly diversity across programming languages and hardware platforms, by applying serverless and modern software engineering approaches. It aims to support practical quantum computing and ease the transition for traditional software engineers into hybrid quantum-classical development.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1031,7 +1016,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>asanopen-source toolundertheGPL-3.0license.</t>
+          <t>Software Availability: We will release the QFaaS framework in open source</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1047,7 +1032,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>itprovidessupportfor externaldatasets,accommodatingbothOpenQASMfilesforquantumtasksandquantumcomputercalibrationdata for quantumsystems.</t>
+          <t>We design QFaaS as a unified quantum computing framework by supporting well-known quantum languages and software development kits (Qiskit, Q#, Cirq, and Braket)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1057,7 +1042,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>OurtoolkitalsofacilitatesdataimportingandexportinginacommonCSVformat, enablingfurther investigationandanalysis.</t>
+          <t>After finishing all the processing, the function handler could return the result to end-users, including the HTTP Status Code and response data in JSON format.</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1067,7 +1052,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Then, whenthesimulationisinitialized,itwillfirstsetuptheenvironmentwithallpre-definedentities.</t>
+          <t>We utilize the DevOps techniques in operating QFaaS, including continuous integration and continuous deployment, which supports to automate the quantum software development cycle, from quantum environment setup to hybrid quantum-classical function deployment.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1077,17 +1062,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Through rigorous empiricalvalidation and evaluations usinglarge-scalequantumworkloaddatasets,wedemonstratetheflexibilityand applicability of our toolkit in various use cases.</t>
+          <t>We present two practical use cases and perform the evaluations on quantum computers and simulators</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>The toolkit follows a layered, modular architecture and was improved through refactoring and feature additions to support both quantum and hybrid quantum-classical simulation. It is designed around discrete-event simulation and resource-management evaluation in cloud-edge hybrid environments.</t>
+          <t>The framework is designed around modularity, with separate pluggable modules responsible for specific functionality so the system can be extended and maintained more easily. It also draws on microservice and XaaS ideas, emphasizing portability, scalability, hybrid quantum-classical support, containerization, and DevOps-based operation.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Implemented using a discrete-event simulation approach and leveraging the core components of the CloudSim toolkit; the design also includes CloudSim-derived classical entities such as VMs, containers, and classical tasks.</t>
+          <t>QFaaS is built using Docker containers and Kubernetes, and integrates DevOps practices such as CI/CD. It supports Qiskit, Q#, Cirq, and Braket, and connects to IBM Quantum and Amazon Braket, with JSON used for standardizing requests and responses.</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1097,7 +1082,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Thegatewaylayercomprisesintermediarycomponents,includinggatewaysandbrokers,whichfacilitatecommunication andtaskorchestrationbetweencloudandedgecomputationcomponents.</t>
+          <t>We employed Kubernetes to orchestrate all the pods (the container-based unit of Kubernetes) for the QFaaS function across all cluster nodes.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1107,21 +1092,29 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Thebrokers,namelyQCloudBroker,QEdgeBroker,CCloudBroker,andCEdgeBroker,thenperformthetaskschedulingbasedontheresourcemanagementpolicies inthesystem.</t>
+          <t>We break down QFaaS into six components: the QFaaS Core APIs and API Gateway, the Application Deployment Layer, the Classical Cloud Layer, the Quantum Cloud Layer, the Monitoring Layer, and the User Interface.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>We design QFaaS as a unified quantum computing framework by supporting well-known quantum languages and software development kits (Qiskit, Q#, Cirq, and Braket), executing the quantum tasks on multiple simulators and quantum cloud providers (IBM Quantum and Amazon Braket).</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>We design QFaaS as a unified quantum computing framework by supporting well-known quantum languages and software development kits (Qiskit, Q#, Cirq, and Braket), executing the quantum tasks on multiple simulators and quantum cloud providers (IBM Quantum and Amazon Braket).</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1135,15 +1128,19 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>WedevelopediQuantumusingthe discrete-eventsimulationapproach,leveragingthecorecomponentsoftheCloudSim toolkit.</t>
+          <t>All quantum SDKs and languages have their built-in quantum simulator, which can run directly inside a pod at the Kubernetes cluster.</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>We will enhance the security and scalability capabilities in QFaaS to support a large number of requests from multiple users.</t>
+        </is>
+      </c>
       <c r="AG4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1151,15 +1148,19 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>adatacentercanbeseenasacollection(orcluster)ofmultiplecomputingnodes(QNodesorCNodes), whichcanbecoordinatedtoperformacommontask.</t>
+          <t>Each function will be run on a pod and could be scaled up horizontally by replicating the original pod.</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>We break down QFaaS into six components: the QFaaS Core APIs and API Gateway, the Application Deployment Layer, the Classical Cloud Layer, the Quantum Cloud Layer, the Monitoring Layer, and the User Interface.</t>
+        </is>
+      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -1167,7 +1168,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>IniQuantum,agateway(cloudoredgegateway)isacommunicationinterfacebetweendatacenterbrokersandthelayerbelow.</t>
+          <t>Our framework also provides multiple ways for users to interact with the core components, including QFaaS Dashboard (a modern web-based application), QFaaS CLI (an interactive command-line tool), and QFaaS Core APIs.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1177,17 +1178,17 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>"For modeling large-scale quantum task workloads, we used MQT Bench34 and extracted features of quantum circuits for 28differentquantumalgorithmsintofoursetsasshowninTable 5."</t>
+          <t>We have implemented two application use cases with QFaaS to validate our proposed design and demonstrate how our framework can facilitate quantum software development in practice.</t>
         </is>
       </c>
       <c r="AO4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_f7bfef4503</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1202,7 +1203,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>staq is a full-stack quantum compiler toolkit designed as a collection of small command-line tools for tasks such as optimization, translation, and physical mapping on quantum devices with restricted connectivity. It aims to provide complex functionality by composing minimalist tools around a single textual language, openQASM.</t>
+          <t>staq is a compiler and software toolkit for the openQASM language whose goal is to provide transformation, optimization, and compilation tools on a common language while targeting different simulation and hardware platforms.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1219,12 +1220,12 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Multiple</t>
+          <t>QI</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>staq also oﬀers some unique features, such as the ability to use and synthesize classical logic, s peciﬁed in an industrial-strength language such as Verilog [17], directly within openQASM code.</t>
+          <t>operating on a single textual language, openQASM [15].</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1234,15 +1235,19 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Finally, staq can generate quantum code in a variety of formats that encompass many of the currently available quantu m platforms [15, 18, 19, 9, 10, 12].</t>
+          <t>Finally, staq can generate quantum code in a variety of formats that encompass many of the currently available quantum platforms [15, 18, 19, 9, 10, 12].</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>staq achieves complex functionality via combining (piping) small tools, each of which performs a single task using the most advanced current state-of-the-art methods.</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
           <t>EX</t>
@@ -1250,17 +1255,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>To assess the performance of staq, we compare it against the well-known software toolkit and compiler Qiskit [19].</t>
+          <t>The remainder of this paper describes the staq toolkit and its functionality and uses cases while providing a set of benchmarks (Section 2),</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>staq follows a UNIX-style design that emphasizes small, single-purpose tools composed through pipelines, and it operates directly on QASM syntax trees with a Clang-inspired visitor-based analysis and transformation approach.</t>
+          <t>The architecture emphasizes a UNIX-style philosophy of composing many small single-purpose tools into larger workflows. It also follows a Clang-style, syntax-tree-based modular compiler design so transformations can be applied independently and combined flexibly.</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>The toolkit is implemented in standard C++ using the C++17 standard, works directly on QASM syntax trees, includes Visitor classes for AST traversal and splicing, and supports classical logic specified in Verilog within openQASM code.</t>
+          <t>Implemented in standard C++ using the C++17 standard, with a Clang-inspired approach based on QASM syntax trees and Visitor classes. It includes source-to-source compiler/transpiler tooling targeting formats such as Quil, ProjectQ, Q#, and Cirq.</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1270,7 +1275,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>staq achieves complex functionality via combining (piping) sma ll tools, each of which performs a single task using the most adv anced current state-of-the-art methods.</t>
+          <t>The main command line compiler staq - oﬀers a ﬂexible pass registration system, whereby passes are given via command-line arguments and are executed in the order given.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1291,10 +1296,14 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Along with the default QASM output, staq includes a suite of source-to-source compilers or "transpilers", currently supporting output to Quil [9], ProjectQ [10], Q# [12], and Cir q [18].</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>Not stated</t>
@@ -1332,7 +1341,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>T ool suite In addition to a single compiler, the staq software package also includes a suite of lightweight command line tools which can be chained together using Unix-st yle pipelines to perform a range of compilation tasks.</t>
+          <t>The main command line compiler staq - oﬀers a ﬂexible pass registration system, whereby passes are given via command-line arguments and are executed in the order given.</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1342,11 +1351,11 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+          <t>"staq currently implements three layout generation algorithms: linear, eager, and best-fit."</t>
         </is>
       </c>
       <c r="AO5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1360,7 +1369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,66 +1397,176 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_f7bfef4503</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>linear</t>
+          <t>LHRS (LUT-based Hierarchical Reversible Logic Synthesis)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>layout generation</t>
+          <t>synthesis</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+          <t>"synthesized over the Cliﬀord group and T gates using the EPFL implementation of the LUT-based Hierarchical Reversible Logic Synthesis (LHRS) framework [23]."</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_f7bfef4503</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eager</t>
+          <t>Gray-synth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>layout generation</t>
+          <t>synthesis</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+          <t>"For these purposes staq includes an optimization pass - CNOT resynthesis to reduce the number of cx (i.e. CNOT) gates in a program by performing the CNOT-dihedral algo rithm Gray-synth of Amy, Azimzadeh, and Mosca [25]."</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_f7bfef4503</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>layout generation</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>"staq currently implements three layout generation algorithms: linear, eager, and best-fit."</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>eager</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>layout generation</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>"staq currently implements three layout generation algorithms: linear, eager, and best-fit."</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>best-fit</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>layout generation</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>staq currently implements three layout generation algorithms: linear, eager, and best-fit.</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>"staq currently implements three layout generation algorithms: linear, eager, and best-fit."</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>permutation-based mapping (swap)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>"staq implements a version of permutation-based mapping (swap) where for a CNOT gate between uncoupled qubits, the endpoints are swapped along the shortest (weight ed) path in the coupling graph until they are adjacent."</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>steiner</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>mapping</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>"Along with the swap mapping algorithm, staq includes a mapping algorithm ( steiner) based on constrained CNOT and CNOT-dihedral synthesis in the style of [34] a nd [35]."</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>constrained Gray-synthesis</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>synthesis</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>"staq performs constrained Gray-synthesis by delaying CNOT gates until a partition of size 1 is reached."</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1500,22 +1619,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>T000</t>
+          <t>T_1cd9410310</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Access to quantum cloud services is limited from the authors' region, restricting which providers they can currently demonstrate with.</t>
+          <t>The framework does not directly simulate quantum physical phenomena such as superposition and entanglement, limiting it to a high-level abstract simulation of operational aspects.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Access</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Due to the current limitation around access to quantum cloud services from our region, we are able to demonstrate the experiments with IBM Quantum and Amazon Braket at the moment.</t>
+          <t>iQuantum's design does not include the direct simulation of quantum physical phenomena such as superposition and entanglement.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1525,29 +1644,29 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Due to the current limitation around access to quantum cloud services from our region, we are able to demonstrate the experiments with IBM Quantum and Amazon Braket at the moment.</t>
+          <t>This decision aligns with our framework's objective to provide a high-level simulation environment primarily concerned with the operational aspects of quantum computing environments.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T000</t>
+          <t>T_1cd9410310</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The diversity of quantum programming languages and hardware platforms creates challenges for quantum software engineering.</t>
+          <t>Resource provisioning policies are mainly focused on classical resources because quantum resource virtualization or partitioning is not yet mature.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Interoperability</t>
+          <t>Scalability</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>However, quantum software engineering is still in its infancy with many challenges, especially dealing with the diversity of quantum programming languages and hardware platforms.</t>
+          <t>It is important to note that resource provisioning policies are mainly for classical resources, as quantum resource virtualization or partitioning is not yet mature.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1557,29 +1676,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>However, quantum software engineering is still in its infancy with many challenges, especially dealing with the diversity of quantum programming languages and hardware platforms.</t>
+          <t>It is important to note that resource provisioning policies are mainly for classical resources, as quantum resource virtualization or partitioning is not yet mature.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_1cd9410310</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Quantum computing has a steep learning curve for developers, making adoption difficult.</t>
+          <t>Circuit depth is only an approximate metric, and a more precise method is recommended for extracting the number of circuit layers when measuring CLOPS for quantum nodes.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
+          <t>However, it is important to note that circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks to adapt to the measurement of the CLOPS metric for quantum nodes.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1589,19 +1708,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
+          <t>However, it is important to note that circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks to adapt to the measurement of the CLOPS metric for quantum nodes.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quantum software platforms and toolkits are difficult to use in industry and provide limited contextual support for generating quantum algorithms.</t>
+          <t>Quantum computing has a steep learning curve due to the paradigm shift from classical computing.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1611,7 +1730,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Quantum software platforms and toolkits are difficult to use in industry.</t>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1621,29 +1740,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>they do not bring much context support to the generation of quantum algorithms.</t>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tool version incompatibilities and discontinued features forced modifications to the platform.</t>
+          <t>Quantum software platforms and toolkits are difficult to use in industry and provide limited context support for generating quantum algorithms.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Maintainability</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Several of the tools we have integrated into QuantumPath have been released in different versions (not always compatible with the previous ones), and some features have been discontinued - with the result that we have had to modify our platform.</t>
+          <t>Quantum software platforms and toolkits are difficult to use in industry.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1653,29 +1772,29 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>with the result that we have had to modify our platform.</t>
+          <t>they do not bring much context support to the generation of quantum algorithms.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Providing integrated design services for both gate-based quantum and annealing systems on one platform has been difficult.</t>
+          <t>Version incompatibilities and discontinued features in integrated tools force modifications to the platform.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Interoperability</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Design services for both gate-based quantum and annealing systems have been difficult to offer on the same platform and in an integrated manner.</t>
+          <t>Several of the tools we have integrated into QuantumPath have been released in different versions (not always compatible with the previous ones), and some features have been discontinued - with the result that we have had to modify our platform.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1685,29 +1804,29 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>have been difficult to offer on the same platform and in an integrated manner.</t>
+          <t>with the result that we have had to modify our platform.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T001</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Annealing-based system design needs a more user-friendly interface to guide users and reduce errors.</t>
+          <t>Providing integrated design services for both gate-based quantum and annealing systems on the same platform is difficult.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Interoperability</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
+          <t>Design services for both gate-based quantum and annealing systems have been difficult to offer on the same platform and in an integrated manner.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1717,29 +1836,29 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>which can guide the user and control possible errors.</t>
+          <t>have been difficult to offer on the same platform and in an integrated manner.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T_523e21620e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>iQuantum does not directly simulate quantum physical phenomena such as superposition and entanglement, limiting it to high-level operational simulation.</t>
+          <t>Annealing-system design needs a user-friendly interface beyond mathematical formula definitions to guide users and prevent errors.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>iQuantum's design does not include the direct simulation of quantum physical phenomena such as superposition and entanglement.</t>
+          <t>it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1749,29 +1868,29 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>This decision aligns with our framework's objective to provide a high-level simulation environment primarily concerned with the operational aspects of quantum computing environments.</t>
+          <t>we believe that it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Evaluating the impact of quantum errors on execution results is outside the scope of the study.</t>
+          <t>Quantum software engineering faces interoperability challenges because of the diversity of quantum programming languages and hardware platforms.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reliability</t>
+          <t>Interoperability</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>supporting the evaluation of the quantum errors impacts on quantum execution results is not within the scope of our study</t>
+          <t>However, quantum software engineering is still in its infancy with many challenges, especially dealing with the diversity of quantum programming languages and hardware platforms.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1781,29 +1900,29 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>However, it is important to note that supporting the evaluation of the quantum errors impacts on quantum execution results is not within the scope of our study and can be considered for future extension.</t>
+          <t>However, quantum software engineering is still in its infancy with many challenges, especially dealing with the diversity of quantum programming languages and hardware platforms.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T002</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Circuit depth is only an approximate metric, so more precise methods are needed for measuring CLOPS-related circuit layers.</t>
+          <t>The field is not yet reliable and must keep adapting to rapid changes in quantum hardware.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Reliability</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks to adapt to the measurement of the CLOPS metric for quantum nodes.</t>
+          <t>As Quantum Software Engineering is still an emerging area of research with numerous challenges, there is a need for significant research effort to make it reliable and simultaneously adapt to rapid advances in quantum hardware.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1813,29 +1932,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>However, it is important to note that circuit depth is only an approximate metric, and we recommend using a more precise method to extract the number of circuit layers in quantum tasks to adapt to the measurement of the CLOPS metric for quantum nodes.</t>
+          <t>As Quantum Software Engineering is still an emerging area of research with numerous challenges, there is a need for significant research effort to make it reliable and simultaneously adapt to rapid advances in quantum hardware.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The scalability of staq's optimization algorithms needs improvement as qubit count increases.</t>
+          <t>Heterogeneity across SDKs, languages, and connection methods makes it difficult for engineers to choose suitable technologies.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scalability</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases.</t>
+          <t>Besides, the variety of current quantum SDKs and the heterogeneous quantum technologies could confuse software engineers in picking an appropriate technique for their software.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1845,61 +1964,61 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases.</t>
+          <t>Besides, the variety of current quantum SDKs and the heterogeneous quantum technologies could confuse software engineers in picking an appropriate technique for their software.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hardware mapping results were mixed, and Qiskit usually produced better CNOT counts than staq.</t>
+          <t>Different SDKs and languages require different environments, syntax, and connection methods, creating interoperability difficulties.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Interoperability</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Qiskit outperformed staq in terms of CNOT counts in the majority of cases.</t>
+          <t>Each SDK and language has different environment configuration requirements, syntax, and methods to connect with the quantum simulator or quantum computer.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Explicit empirical</t>
+          <t>Implicit anecdotal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>the experimental results for hardware mapping were mixed.</t>
+          <t>Each SDK and language has different environment configuration requirements, syntax, and methods to connect with the quantum simulator or quantum computer.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Some benchmark circuits could not be included because only circuits that fit on IBM's 20-qubit Tokyo chip were reported.</t>
+          <t>Quantum software engineering lacks widely accepted standards and lifecycle practices comparable to mature traditional software processes.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scalability</t>
+          <t>Maintainability</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>only the benchmark circuits which ﬁt onto the chip are re ported in Table 2.</t>
+          <t>Additionally, there is no wellknown standardization or life cycle in quantum software engineering similar to practices like Agile and DevOps in the traditional realm [54].</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1909,39 +2028,1114 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IBM's 20 qubit Tokyo chip was se lected as the target architecture, and as such only the benchmark circuits which ﬁt onto the chip are re ported in Table 2.</t>
+          <t>Additionally, there is no wellknown standardization or life cycle in quantum software engineering similar to practices like Agile and DevOps in the traditional realm [54].</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T003</t>
+          <t>T_b9198d13c7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Local ancilla allocation is non-standard QASM and is not supported by most QPUs.</t>
+          <t>Regional limitations in access to quantum cloud services restrict which providers the framework can currently demonstrate.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Access</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Due to the current limitation around access to quantum cloud services from our region, we are able to demonstrate the experiments with IBM Quantum and Amazon Braket at the moment.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Due to the current limitation around access to quantum cloud services from our region, we are able to demonstrate the experiments with IBM Quantum and Amazon Braket at the moment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T_b9198d13c7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The immaturity and lack of standardization in the field mean more work is needed to keep pace with growing quantum hardware capabilities.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Due to the immature development and lack of standardization, more efforts are still needed to advance this field and adapt to quantum hardware's continuous growth.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Due to the immature development and lack of standardization, more efforts are still needed to advance this field and adapt to quantum hardware's continuous growth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T_b9198d13c7</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Waiting for remote quantum execution can be very long because of queueing, transpilation, and execution delays on NISQ-era cloud backends.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>This waiting time at the quantum cloud provider could be very long (for queuing, transpiling, and executing) due to the current NISQ nature.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>This waiting time at the quantum cloud provider could be very long (for queuing, transpiling, and executing) due to the current NISQ nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Some optimization routines may become prohibitively expensive because repeated simplification to a fixpoint can make runtime quadratic in program length.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In some cases this extra cos t making the optimization quadratic in the length of the program - may b e prohibitive.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>In some cases this extra cos t making the optimization quadratic in the length of the program - may b e prohibitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Scalability of the optimization algorithms remains an open issue as the number of qubits grows.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>It remains a focus of future work to im prove the scalability of staq's optimization algorithms as the number of qubits increases.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Explicit empirical</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>The best results in either case are identiﬁed in bold. For circuit optimizatio n, staq beats Qiskit</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Hardware mapping quality is inconsistent, with mixed benchmark results and worse CNOT counts than Qiskit in most cases.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>While the Steiner mapping algorithm with best-fit initial layout was consistently orders of magnitude faster than Qisk it's default mapping algorithm, Qiskit outperformed staq in terms of CNOT counts in the majority of cases.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Explicit empirical</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>the experimental results for hardware mapping were mixed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The current layout optimization may get trapped in local minima, and more sophisticated search methods may be needed.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>It remains to be seen whether more sophisticated layout optimization a lgorithms which avoid local minima for instance, simulated annealing - can improve the results further .</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>It remains to be seen whether more sophisticated layout optimization a lgorithms which avoid local minima for instance, simulated annealing - can improve the results further .</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Support for local ancilla allocation is limited by non-standard QASM and poor compatibility with most QPUs, requiring automatic ancilla management during compilation.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Interoperability</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs, staq performs automatic ancilla management during the inlining phase of co mpilation.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>tool_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>field_path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>quote</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>overview.input_instruction</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>itprovidessupportfor externaldatasets,accommodatingbothOpenQASMfilesforquantumtasksandquantumcomputercalibrationdatafor quantumsystems.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>overview.output_type</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OurtoolkitalsofacilitatesdataimportingandexportinginacommonCSVformat, enablingfurther investigationandanalysis.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>architecture.simulation_support</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WedevelopediQuantumusingthe discrete-eventsimulationapproach,leveragingthecorecomponentsoftheCloudSim toolkit.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>challenges.challenges[0].category_evidence</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reliability</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>iQuantum's design does not include the direct simulation of quantum physical phenomena such as superposition and entanglement.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>challenges.challenges[0].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>This decision aligns with our framework's objective to provide a high-level simulation environment primarily concerned with the operational aspects of quantum computing environments.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>challenges.challenges[1].category_evidence</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Scalability</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>It is important to note that resource provisioning policies are mainly for classical resources, as quantum resource virtualization or partitioning is not yet mature.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>T_1cd9410310</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>challenges.challenges[1].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>It is important to note that resource provisioning policies are mainly for classical resources, as quantum resource virtualization or partitioning is not yet mature.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>overview.output_type</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>QSC</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>both the circuit editor and the annealing editor generate a proprietary metalanguage</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>overview.automation_level</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>The corresponding metalanguage is then transpiled in design time to the programming language supported by each manufacturer and executed in the target environment.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>overview.evaluation_type</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>IM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>QuantumPath has been tested in recent months by a limited number of customers, invited from the health and finance sectors.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>architecture.orchestrator</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>"Flow":"BoxFlows"</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>architecture.manager_controller</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>architecture.vendor_agnostic_layer</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Finally,wewouldliketohighlightanothersignificantissuewhendecidingonwhichcomputeritismoreconvenientto runaquantumprogram,astheydifferinefficiency,errortolerance,andcost,andmuchdependsonthetypeofalgorithm orcircuittobeexecuted.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>architecture.backend_integration</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs,</t>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>architecture.simulation_support</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>"Device":"dwave_ExactSolver_simulator"</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>architecture.telemetry_monitoring</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Thisbackendmanagestheapproved connectionsofquantumsimulatorsandquantumcomputerstosuppliers;andwillalsocollectallthetelemetryfrom theprocess,</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>algorithms.overall_evidence</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>"walkingtheuserthroughtwoexamplesofquantum-gatesbasedcircuitdesignand annealing-basedoptimisation"</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>quote shorter than 4 words</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>challenges.challenges[0].category_evidence</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>challenges.challenges[0].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Implicit anecdotal</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>As local ancilla allocation is non-standard QASM and moreover not sup ported by most QPUs,</t>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>we have to recognise that the learning curve of quantum computing is very pronounced.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>challenges.challenges[1].category_evidence</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Quantum software platforms and toolkits are difficult to use in industry.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>challenges.challenges[1].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>they do not bring much context support to the generation of quantum algorithms.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>challenges.challenges[2].category_evidence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Maintainability</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Several of the tools we have integrated into QuantumPath have been released in different versions (not always compatible with the previous ones), and some features have been discontinued - with the result that we have had to modify our platform.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>challenges.challenges[2].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>with the result that we have had to modify our platform.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>challenges.challenges[3].category_evidence</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Interoperability</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Design services for both gate-based quantum and annealing systems have been difficult to offer on the same platform and in an integrated manner.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>challenges.challenges[3].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>have been difficult to offer on the same platform and in an integrated manner.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>challenges.challenges[4].category_evidence</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Usability</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>T_523e21620e</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>challenges.challenges[4].strength_evidence</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Implicit anecdotal</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>we believe that it is essential to offer a user-friendly interface beyond the definitions of the mathematical formulae, which can guide the user and control possible errors.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>overview.output_type</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>QSC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Finally, staq can generate quantum code in a variety of formats that encompass many of the currently available quantum platforms [15, 18, 19, 9, 10, 12].</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>overview.automation_level</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>staq achieves complex functionality via combining (piping) small tools, each of which performs a single task using the most advanced current state-of-the-art methods.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>T_f7bfef4503</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>algorithms.algorithms[0].evidence</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>LHRS (LUT-based Hierarchical Reversible Logic Synthesis)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>"synthesized over the Cliﬀord group and T gates using the EPFL implementation of the LUT-based Hierarchical Reversible Logic Synthesis (LHRS) framework [23]."</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>quote not found verbatim in source</t>
         </is>
       </c>
     </row>
